--- a/tools/data_source/game_data.xlsx
+++ b/tools/data_source/game_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AdvanceFour\tools\data_source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AdvanceFour\tools\data_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC2F8DE-B53A-4100-BDB9-2C4574A051F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356D87B6-0363-49B9-997B-1606B8C2E074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Energy" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Function" sheetId="5" r:id="rId5"/>
     <sheet name="Core" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -163,20 +176,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -199,11 +219,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -504,7 +525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -514,7 +535,7 @@
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -575,7 +596,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -585,7 +606,7 @@
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -647,11 +668,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="34.5" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="10" width="10" customWidth="1"/>
@@ -660,7 +681,7 @@
     <col min="15" max="15" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +728,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -764,17 +785,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="34.5" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -803,7 +824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -840,17 +861,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -873,7 +894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -895,6 +916,9 @@
       <c r="G2" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5">
+      <c r="B3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -905,16 +929,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="3" max="3" width="48.375" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,7 +961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>40</v>
       </c>

--- a/tools/data_source/game_data.xlsx
+++ b/tools/data_source/game_data.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energy" sheetId="1" r:id="R5b231fa8dc53463f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propulsion" sheetId="2" r:id="R0f865133d2f84446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon" sheetId="3" r:id="Rc99dbbe815c84a47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defense" sheetId="4" r:id="Re517e50d80604417"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Function" sheetId="5" r:id="R6554a5295d8e45b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core" sheetId="6" r:id="R9076678c438442b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energy" sheetId="1" r:id="Rb7ac04d70fb4408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propulsion" sheetId="2" r:id="Rae807c20b4804282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon" sheetId="3" r:id="Red2e815dd7544870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defense" sheetId="4" r:id="R55e47db90030445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Function" sheetId="5" r:id="Re2087cd3c8094683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core" sheetId="6" r:id="R70d3ffd9f8854fb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -286,14 +286,14 @@
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="7.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="10" t="str">
         <x:v>标识</x:v>
       </x:c>
@@ -304,22 +304,20 @@
         <x:v>描述</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>宽度</x:v>
+        <x:v>高X宽</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>高度</x:v>
+        <x:v>能耗</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>能耗</x:v>
+        <x:v>贴图路径</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>贴图路径</x:v>
-      </x:c>
-      <x:c r="H1" s="10" t="str">
         <x:v>能量输出</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="H1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>energy_smallreactor</x:v>
       </x:c>
@@ -329,22 +327,21 @@
       <x:c r="C2" s="11" t="str">
         <x:v>基础能量模块，为飞船提供持续能量。</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
-        <x:v>1</x:v>
+      <x:c r="D2" s="11" t="str">
+        <x:v>1x1</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>res://data/assets/modules/energy_smallreactor.png</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="n">
+      <x:c r="G2" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-    </x:row>
+      <x:c r="H2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -357,14 +354,14 @@
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4.25" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="4.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="10" t="str">
         <x:v>标识</x:v>
       </x:c>
@@ -375,22 +372,20 @@
         <x:v>描述</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>宽度</x:v>
+        <x:v>高X宽</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>高度</x:v>
+        <x:v>能耗</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>能耗</x:v>
+        <x:v>贴图路径</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>贴图路径</x:v>
-      </x:c>
-      <x:c r="H1" s="10" t="str">
         <x:v>推力</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="H1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>propulsion_smallengine</x:v>
       </x:c>
@@ -400,22 +395,21 @@
       <x:c r="C2" s="11" t="str">
         <x:v>基础动力模块，为飞船提供主要推进力。</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
-        <x:v>1</x:v>
+      <x:c r="D2" s="11" t="str">
+        <x:v>1x1</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>res://data/assets/modules/propulsion_smallengine.png</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="n">
+      <x:c r="G2" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-    </x:row>
+      <x:c r="H2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -428,21 +422,24 @@
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="7.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="7.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="7.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15.25" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="9.75" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="41.880001068115234" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15.25" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="41.880001068115234" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="10" t="str">
         <x:v>标识</x:v>
       </x:c>
@@ -453,43 +450,52 @@
         <x:v>描述</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>宽度</x:v>
+        <x:v>高X宽</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>高度</x:v>
+        <x:v>能耗</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>能耗</x:v>
+        <x:v>贴图路径</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>贴图路径</x:v>
+        <x:v>火力</x:v>
       </x:c>
       <x:c r="H1" s="10" t="str">
-        <x:v>火力</x:v>
+        <x:v>攻击范围</x:v>
       </x:c>
       <x:c r="I1" s="10" t="str">
-        <x:v>攻击范围</x:v>
+        <x:v>射击间隔</x:v>
       </x:c>
       <x:c r="J1" s="10" t="str">
-        <x:v>射击间隔</x:v>
+        <x:v>炮塔转速（度/秒）</x:v>
       </x:c>
       <x:c r="K1" s="10" t="str">
-        <x:v>炮塔转速（度/秒）</x:v>
+        <x:v>弹速</x:v>
       </x:c>
       <x:c r="L1" s="10" t="str">
-        <x:v>弹速</x:v>
+        <x:v>开火角容差（度）</x:v>
       </x:c>
       <x:c r="M1" s="10" t="str">
-        <x:v>开火角容差（度）</x:v>
+        <x:v>射界（度）</x:v>
       </x:c>
       <x:c r="N1" s="10" t="str">
-        <x:v>射界（度）</x:v>
+        <x:v>炮塔贴图路径</x:v>
       </x:c>
       <x:c r="O1" s="10" t="str">
-        <x:v>炮塔贴图路径</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+        <x:v>炮塔高X宽</x:v>
+      </x:c>
+      <x:c r="P1" s="10" t="str">
+        <x:v>炮塔轴点</x:v>
+      </x:c>
+      <x:c r="Q1" s="10" t="str">
+        <x:v>炮口</x:v>
+      </x:c>
+      <x:c r="R1" s="10" t="str">
+        <x:v>炮塔素材转角（度）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>weapon_cannon</x:v>
       </x:c>
@@ -499,43 +505,53 @@
       <x:c r="C2" s="11" t="str">
         <x:v>基础武器模块，提供稳定的常规火力。</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
-        <x:v>1</x:v>
+      <x:c r="D2" s="11" t="str">
+        <x:v>1x1</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>res://data/assets/modules/weapon_cannon_base.png</x:v>
       </x:c>
+      <x:c r="G2" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="H2" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>500</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J2" s="11" t="n">
-        <x:v>0.5</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K2" s="11" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M2" s="11" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="L2" s="11" t="n">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="M2" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="N2" s="11" t="n">
-        <x:v>180</x:v>
+      <x:c r="N2" s="11" t="str">
+        <x:v>res://data/assets/modules/weapon_cannon_turret.png</x:v>
       </x:c>
       <x:c r="O2" s="11" t="str">
-        <x:v>res://data/assets/modules/weapon_cannon_turret.png</x:v>
-      </x:c>
-    </x:row>
+        <x:v>2x1</x:v>
+      </x:c>
+      <x:c r="P2" s="11" t="str">
+        <x:v>0.5,0.25</x:v>
+      </x:c>
+      <x:c r="Q2" s="11" t="str">
+        <x:v>0.5,0.98</x:v>
+      </x:c>
+      <x:c r="R2" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -548,15 +564,15 @@
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="6" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="4.25" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="4.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="10" t="str">
         <x:v>标识</x:v>
       </x:c>
@@ -567,25 +583,23 @@
         <x:v>描述</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>宽度</x:v>
+        <x:v>高X宽</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>高度</x:v>
+        <x:v>能耗</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>能耗</x:v>
+        <x:v>贴图路径</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>贴图路径</x:v>
+        <x:v>生命值</x:v>
       </x:c>
       <x:c r="H1" s="10" t="str">
-        <x:v>生命值</x:v>
-      </x:c>
-      <x:c r="I1" s="10" t="str">
         <x:v>防护</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="I1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>defense_lightarmor</x:v>
       </x:c>
@@ -595,25 +609,24 @@
       <x:c r="C2" s="11" t="str">
         <x:v>基础防护模块，为飞船提供结构防护。</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
+      <x:c r="D2" s="11" t="str">
+        <x:v>1x1</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>res://data/assets/modules/defense_lightarmor.png</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
-        <x:v>res://data/assets/modules/defense_lightarmor.png</x:v>
-      </x:c>
-      <x:c r="H2" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
+      <x:c r="I2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -626,14 +639,14 @@
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="7.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="10" t="str">
         <x:v>标识</x:v>
       </x:c>
@@ -644,22 +657,20 @@
         <x:v>描述</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>宽度</x:v>
+        <x:v>高X宽</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>高度</x:v>
+        <x:v>能耗</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>能耗</x:v>
+        <x:v>贴图路径</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>贴图路径</x:v>
-      </x:c>
-      <x:c r="H1" s="10" t="str">
         <x:v>仓储容量</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="H1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>function_radar</x:v>
       </x:c>
@@ -669,23 +680,21 @@
       <x:c r="C2" s="11" t="str">
         <x:v>基础功能模块。现阶段暂无额外参数。</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
-        <x:v>1</x:v>
+      <x:c r="D2" s="11" t="str">
+        <x:v>1x1</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>res://data/assets/modules/function_radar.png</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="n">
+      <x:c r="G2" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
+      <x:c r="H2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="11" t="str">
         <x:v>function_cargo_hold</x:v>
       </x:c>
@@ -695,21 +704,19 @@
       <x:c r="C3" s="11" t="str">
         <x:v>2×2 仓储模块，为当前 Run 提供 16 点模块仓储容量。</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="n">
-        <x:v>2</x:v>
+      <x:c r="D3" s="11" t="str">
+        <x:v>2x2</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>res://data/assets/modules/function_cargo_hold.png</x:v>
       </x:c>
-      <x:c r="H3" s="11" t="n">
+      <x:c r="G3" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
+      <x:c r="H3" s="11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -723,13 +730,13 @@
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="10" t="str">
         <x:v>标识</x:v>
       </x:c>
@@ -740,19 +747,17 @@
         <x:v>描述</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>宽度</x:v>
+        <x:v>高X宽</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>高度</x:v>
+        <x:v>能耗</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>能耗</x:v>
-      </x:c>
-      <x:c r="G1" s="10" t="str">
         <x:v>贴图路径</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="G1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>core_bridge</x:v>
       </x:c>
@@ -762,19 +767,18 @@
       <x:c r="C2" s="11" t="str">
         <x:v>飞船核心区域。核心模块被击毁时，飞船判定为沉没。</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
-        <x:v>2</x:v>
+      <x:c r="D2" s="11" t="str">
+        <x:v>2x2</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>res://data/assets/modules/core_bridge.png</x:v>
       </x:c>
-    </x:row>
+      <x:c r="G2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/tools/data_source/game_data.xlsx
+++ b/tools/data_source/game_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AdvanceFour\tools\data_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4169FCB4-B852-4552-B171-68102C5761B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B53910-B00C-4853-BC99-D07813A52333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,7 +630,7 @@
     <col min="13" max="13" width="9.75" customWidth="1"/>
     <col min="14" max="14" width="46.25" customWidth="1"/>
     <col min="15" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="25" customWidth="1"/>
+    <col min="18" max="18" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1">
@@ -742,7 +742,7 @@
         <v>36</v>
       </c>
       <c r="R2" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1"/>
